--- a/results/tables/01_contamination_assessment/table2_rda_axes_summary.xlsx
+++ b/results/tables/01_contamination_assessment/table2_rda_axes_summary.xlsx
@@ -470,19 +470,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02084429707536857</v>
+        <v>0.3899076180170279</v>
       </c>
       <c r="D2" t="n">
-        <v>36.07490285965252</v>
+        <v>37.99720520911572</v>
       </c>
       <c r="E2" t="n">
-        <v>36.07490285965252</v>
+        <v>37.99720520911572</v>
       </c>
       <c r="F2" t="n">
-        <v>2.69382670734596</v>
+        <v>3.115390756913293</v>
       </c>
       <c r="G2" t="n">
-        <v>0.304</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="3">
@@ -495,19 +495,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01322022703574617</v>
+        <v>0.2269011862206224</v>
       </c>
       <c r="D3" t="n">
-        <v>22.88004265016274</v>
+        <v>22.11193251074219</v>
       </c>
       <c r="E3" t="n">
-        <v>58.95494550981526</v>
+        <v>60.10913771985791</v>
       </c>
       <c r="F3" t="n">
-        <v>1.70852490430841</v>
+        <v>1.812957289420074</v>
       </c>
       <c r="G3" t="n">
-        <v>0.87</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="4">
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.008763084885069689</v>
+        <v>0.1757518879441827</v>
       </c>
       <c r="D4" t="n">
-        <v>15.16613560230544</v>
+        <v>17.12734053791424</v>
       </c>
       <c r="E4" t="n">
-        <v>74.12108111212071</v>
+        <v>77.23647825777215</v>
       </c>
       <c r="F4" t="n">
-        <v>1.132503150227868</v>
+        <v>1.404270606447745</v>
       </c>
       <c r="G4" t="n">
-        <v>0.998</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="5">
@@ -545,19 +545,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.00728709915895182</v>
+        <v>0.1357000060453893</v>
       </c>
       <c r="D5" t="n">
-        <v>12.61166991322945</v>
+        <v>13.22421193719718</v>
       </c>
       <c r="E5" t="n">
-        <v>86.73275102535015</v>
+        <v>90.46069019496933</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9417531453559747</v>
+        <v>1.084253102560363</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="6">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.004422960729287801</v>
+        <v>0.06125025031496053</v>
       </c>
       <c r="D6" t="n">
-        <v>7.654749790035509</v>
+        <v>5.968948086122341</v>
       </c>
       <c r="E6" t="n">
-        <v>94.38750081538566</v>
+        <v>96.42963828109167</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5716042951708491</v>
+        <v>0.4893940381578287</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.003242935976695577</v>
+        <v>0.03663720069982278</v>
       </c>
       <c r="D7" t="n">
-        <v>5.612499184614347</v>
+        <v>3.570361718908319</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4191030051360526</v>
+        <v>0.2927339481077295</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
